--- a/data_mahasiswa_dummy.xlsx
+++ b/data_mahasiswa_dummy.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ana Kusmawati</t>
+          <t>Jagapati Prasetya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -496,7 +496,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2005-03-14</t>
+          <t>2008-08-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -504,24 +504,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>36</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2701001</t>
+          <t>2602001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Siska Widiastuti</t>
+          <t>Julia Nasyidah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,11 +528,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2005-06-19</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -547,30 +545,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2603001</t>
+          <t>2702001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raden Nababan</t>
+          <t>Cindy Mulyani</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2005-02-21</t>
+          <t>2005-12-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -578,19 +576,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>37</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2602001</t>
+          <t>2602002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Daliman Pratama</t>
+          <t>Hilda Wijayanti</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -600,7 +596,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -608,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2006-05-25</t>
+          <t>2007-09-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -616,29 +612,27 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>18</v>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2602002</t>
+          <t>2601001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Soleh Prasasta</t>
+          <t>Kani Hastuti</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -654,29 +648,27 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>12</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2703001</t>
+          <t>2704001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nrima Maheswara</t>
+          <t>Rini Usada</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -684,7 +676,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2006-12-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -692,37 +684,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>36</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2701002</t>
+          <t>2502001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ratna Zulaika</t>
+          <t>Ivan Prakasa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2007-01-24</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,37 +720,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>20</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2704001</t>
+          <t>2601002</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bakti Januar</t>
+          <t>Aisyah Usamah</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2007-06-25</t>
+          <t>2006-05-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -768,24 +756,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>39</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2702001</t>
+          <t>2601003</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teddy Napitupulu</t>
+          <t>Banawi Rajata</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -794,11 +780,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2005-12-31</t>
+          <t>2005-02-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -806,19 +792,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>46</v>
-      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2703002</t>
+          <t>2603001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kani Fujiati</t>
+          <t>Yessi Winarsih</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -832,11 +816,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2007-07-30</t>
+          <t>2006-07-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -844,29 +828,27 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>9</v>
-      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2601001</t>
+          <t>2604001</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gilda Farida</t>
+          <t>Malik Dabukke</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -874,7 +856,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2006-08-29</t>
+          <t>2006-06-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -882,19 +864,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2702002</t>
+          <t>2502002</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ega Pradana</t>
+          <t>Rachel Yuliarti</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -904,15 +884,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2008-09-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -920,37 +900,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>17</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2703003</t>
+          <t>2602003</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zulaikha Hasanah</t>
+          <t>Daliman Firmansyah</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2007-03-18</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -963,30 +941,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2501001</t>
+          <t>2703001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Darimin Situmorang</t>
+          <t>Paramita Padmasari</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2007-06-21</t>
+          <t>2008-02-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -994,37 +972,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>35</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2504001</t>
+          <t>2703002</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hani Wulandari</t>
+          <t>Arsipatra Pradana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2007-02-17</t>
+          <t>2008-01-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1032,24 +1008,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>23</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2702003</t>
+          <t>2701001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Salsabila Padmasari</t>
+          <t>Intan Namaga</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1062,7 +1036,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2008-08-17</t>
+          <t>2006-05-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1070,24 +1044,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H17" t="n">
-        <v>26</v>
-      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2704002</t>
+          <t>2701002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Widya Mardhiyah</t>
+          <t>Jessica Maryati</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1100,7 +1072,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2008-04-18</t>
+          <t>2005-12-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1108,24 +1080,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>8</v>
-      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2703004</t>
+          <t>2601004</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Limar Suwarno</t>
+          <t>Digdaya Siregar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1134,11 +1104,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
+          <t>2005-09-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1146,19 +1116,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H19" t="n">
-        <v>25</v>
-      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2504002</t>
+          <t>2504001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Talia Laksmiwati</t>
+          <t>Hadi Siregar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1168,7 +1136,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1176,7 +1144,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2008-11-06</t>
+          <t>2005-06-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1184,19 +1152,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>13</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2602003</t>
+          <t>2702002</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anita Anggraini</t>
+          <t>Sakti Saefullah</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1206,15 +1172,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2005-03-15</t>
+          <t>2006-09-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1222,37 +1188,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H21" t="n">
-        <v>14</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2704003</t>
+          <t>2503002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kiandra Kuswandari</t>
+          <t>Cagak Anggriawan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2007-02-15</t>
+          <t>2007-12-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1260,37 +1224,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>21</v>
-      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2601002</t>
+          <t>2504002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Indah Permata</t>
+          <t>Cager Jailani</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2006-03-09</t>
+          <t>2006-02-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1298,37 +1260,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H23" t="n">
-        <v>47</v>
-      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2602004</t>
+          <t>2504003</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fathonah Oktaviani</t>
+          <t>Malik Tarihoran</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2006-03-18</t>
+          <t>2007-10-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1336,29 +1296,27 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H24" t="n">
-        <v>19</v>
-      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2704004</t>
+          <t>2703003</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ratna Wijayanti</t>
+          <t>Martaka Sirait</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1366,7 +1324,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2006-03-08</t>
+          <t>2006-05-03</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1374,24 +1332,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H25" t="n">
-        <v>8</v>
-      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2501002</t>
+          <t>2603002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Carla Aryani</t>
+          <t>Oliva Agustina</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1400,11 +1356,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2005-01-19</t>
+          <t>2006-12-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1412,19 +1368,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>37</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2501003</t>
+          <t>2701003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hani Usamah</t>
+          <t>Maman Prayoga</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1434,15 +1388,15 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2006-11-12</t>
+          <t>2007-06-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1455,12 +1409,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2502001</t>
+          <t>2602004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kuncara Napitupulu</t>
+          <t>Kurnia Suwarno</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1474,11 +1428,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2004-11-30</t>
+          <t>2007-11-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1486,37 +1440,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>21</v>
-      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2703005</t>
+          <t>2502003</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rahayu Maryati</t>
+          <t>Prabowo Budiyanto</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2005-12-10</t>
+          <t>2006-11-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1524,24 +1476,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H29" t="n">
-        <v>42</v>
-      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2601003</t>
+          <t>2502004</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bambang Winarno</t>
+          <t>Jarwa Natsir</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1550,11 +1500,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2007-05-19</t>
+          <t>2007-10-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1562,29 +1512,27 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>9</v>
-      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2504003</t>
+          <t>2502005</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jelita Usada</t>
+          <t>Gara Januar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1592,7 +1540,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2007-09-10</t>
+          <t>2006-09-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1600,24 +1548,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>28</v>
-      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2702004</t>
+          <t>2703004</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wardi Prayoga</t>
+          <t>Respati Tarihoran</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1630,7 +1576,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2007-01-27</t>
+          <t>2008-09-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1638,19 +1584,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>33</v>
-      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2701003</t>
+          <t>2601005</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tina Mayasari</t>
+          <t>Vanesa Oktaviani</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1664,11 +1608,11 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2008-05-30</t>
+          <t>2008-08-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1676,37 +1620,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H33" t="n">
-        <v>17</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2701004</t>
+          <t>2502006</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kiandra Maryati</t>
+          <t>Dodo Widodo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>2006-10-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1714,19 +1656,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>35</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2502002</t>
+          <t>2702003</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Balamantri Wacana</t>
+          <t>Luwes Sitorus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1740,11 +1680,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2006-02-19</t>
+          <t>2007-11-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1752,37 +1692,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H35" t="n">
-        <v>22</v>
-      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2501004</t>
+          <t>2703005</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teguh Habibi</t>
+          <t>Ophelia Agustina</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2006-12-21</t>
+          <t>2006-03-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1790,37 +1728,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H36" t="n">
-        <v>32</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2701005</t>
+          <t>2604002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wulan Winarsih</t>
+          <t>Hendra Haryanto</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2007-05-31</t>
+          <t>2008-08-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1828,24 +1764,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H37" t="n">
-        <v>42</v>
-      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2604001</t>
+          <t>2603003</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aris Suwarno</t>
+          <t>Rizki Prasetya</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1858,7 +1792,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2008-05-25</t>
+          <t>2007-03-07</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1866,37 +1800,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H38" t="n">
-        <v>6</v>
-      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2504004</t>
+          <t>2702004</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Paiman Prasetya</t>
+          <t>Lidya Haryanti</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2006-02-08</t>
+          <t>2005-01-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1904,24 +1836,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H39" t="n">
-        <v>9</v>
-      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2502003</t>
+          <t>2501001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hafshah Mayasari</t>
+          <t>Titi Yuniar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1934,7 +1864,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2005-12-04</t>
+          <t>2006-11-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1947,22 +1877,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2701006</t>
+          <t>2703006</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vivi Wijayanti</t>
+          <t>Edi Samosir</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1970,7 +1900,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2008-06-23</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1978,24 +1908,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H41" t="n">
-        <v>25</v>
-      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2601004</t>
+          <t>2703007</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Paiman Pradipta</t>
+          <t>Argono Simanjuntak</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2004,11 +1932,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2008-07-16</t>
+          <t>2006-02-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2016,24 +1944,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H42" t="n">
-        <v>50</v>
-      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2502004</t>
+          <t>2603004</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yance Puspasari</t>
+          <t>Carla Sudiati</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2042,11 +1968,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2007-05-16</t>
+          <t>2005-12-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2054,24 +1980,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>38</v>
-      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2503002</t>
+          <t>2601006</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Suci Sudiati</t>
+          <t>Victoria Kuswandari</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2080,11 +2004,11 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2008-01-07</t>
+          <t>2006-06-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2092,19 +2016,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>42</v>
-      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2601005</t>
+          <t>2601007</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zelaya Hasanah</t>
+          <t>Rina Widiastuti</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2122,7 +2044,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2005-09-10</t>
+          <t>2006-06-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2130,29 +2052,27 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H45" t="n">
-        <v>3</v>
-      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2604002</t>
+          <t>2603005</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wage Utama</t>
+          <t>Keisha Winarsih</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2160,7 +2080,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2007-01-09</t>
+          <t>2006-07-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2168,37 +2088,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H46" t="n">
-        <v>34</v>
-      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2503003</t>
+          <t>2604003</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Usman Pradipta</t>
+          <t>Cinta Pudjiastuti</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2008-06-10</t>
+          <t>2006-08-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2206,24 +2124,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H47" t="n">
-        <v>46</v>
-      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2701007</t>
+          <t>2602005</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Melinda Mayasari</t>
+          <t>Rika Usamah</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2232,11 +2148,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2007-08-29</t>
+          <t>2007-05-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2244,24 +2160,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H48" t="n">
-        <v>35</v>
-      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2501005</t>
+          <t>2503003</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gatot Firmansyah</t>
+          <t>Galar Firgantoro</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2274,7 +2188,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2006-01-28</t>
+          <t>2005-05-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2282,19 +2196,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>14</v>
-      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2504005</t>
+          <t>2604004</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Elma Hasanah</t>
+          <t>Talia Rahimah</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2308,11 +2220,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2006-06-22</t>
+          <t>2006-07-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2320,24 +2232,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H50" t="n">
-        <v>36</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2502005</t>
+          <t>2701004</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Caraka Adriansyah</t>
+          <t>Rafi Gunawan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2346,11 +2256,11 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2008-03-31</t>
+          <t>2006-01-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2363,17 +2273,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2501006</t>
+          <t>2704002</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nasab Jailani</t>
+          <t>Argono Sitorus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2382,11 +2292,11 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2005-12-04</t>
+          <t>2007-02-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2399,12 +2309,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2602005</t>
+          <t>2602006</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Latika Mandasari</t>
+          <t>Gilda Lestari</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2422,7 +2332,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2007-08-03</t>
+          <t>2007-06-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2430,19 +2340,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H53" t="n">
-        <v>26</v>
-      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2602006</t>
+          <t>2502007</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Galiono Mahendra</t>
+          <t>Adinata Jailani</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2456,11 +2364,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2005-07-17</t>
+          <t>2007-10-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2468,24 +2376,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H54" t="n">
-        <v>28</v>
-      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2601006</t>
+          <t>2603006</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alika Kuswandari</t>
+          <t>Rina Mandasari</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2498,7 +2404,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2006-07-17</t>
+          <t>2008-06-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2511,12 +2417,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2702005</t>
+          <t>2602007</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gamanto Damanik</t>
+          <t>Adiarja Wahyudin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2530,11 +2436,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2008-05-31</t>
+          <t>2006-06-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2542,24 +2448,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>38</v>
-      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2602007</t>
+          <t>2701005</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clara Wijayanti</t>
+          <t>Ulya Wulandari</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2568,11 +2472,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2005-01-11</t>
+          <t>2008-06-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2580,19 +2484,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H57" t="n">
-        <v>44</v>
-      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2503004</t>
+          <t>2603007</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Perkasa Megantara</t>
+          <t>Queen Safitri</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2602,15 +2504,15 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2007-12-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2618,9 +2520,7 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>10</v>
-      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2630,7 +2530,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cinta Wastuti</t>
+          <t>Sabri Latupono</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2640,7 +2540,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2648,7 +2548,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2006-08-22</t>
+          <t>2007-06-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2656,24 +2556,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H59" t="n">
-        <v>35</v>
-      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2504006</t>
+          <t>2501002</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Maria Purwanti</t>
+          <t>Faizah Uyainah</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2686,7 +2584,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2006-12-06</t>
+          <t>2008-11-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2694,19 +2592,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H60" t="n">
-        <v>22</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2704005</t>
+          <t>2704003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mila Prastuti</t>
+          <t>Ciaobella Rahmawati</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2724,7 +2620,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2008-09-29</t>
+          <t>2007-03-07</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2732,24 +2628,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H61" t="n">
-        <v>39</v>
-      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2602009</t>
+          <t>2704004</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ayu Namaga</t>
+          <t>Chelsea Uyainah</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2758,11 +2652,11 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2007-07-09</t>
+          <t>2006-09-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2770,29 +2664,27 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H62" t="n">
-        <v>23</v>
-      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2502006</t>
+          <t>2501003</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mala Laksmiwati</t>
+          <t>Ajimat Uwais</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2800,7 +2692,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2007-09-29</t>
+          <t>2005-12-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2813,17 +2705,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2601007</t>
+          <t>2502008</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wahyu Winarno</t>
+          <t>Aswani Wasita</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2832,11 +2724,11 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2007-06-13</t>
+          <t>2008-05-05</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2844,37 +2736,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H64" t="n">
-        <v>49</v>
-      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2604003</t>
+          <t>2701006</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nasrullah Situmorang</t>
+          <t>Kiandra Winarsih</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2005-11-13</t>
+          <t>2007-11-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2882,19 +2772,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H65" t="n">
-        <v>4</v>
-      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2702006</t>
+          <t>2702005</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kezia Palastri</t>
+          <t>Jindra Mahendra</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2904,7 +2792,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2912,7 +2800,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2006-12-06</t>
+          <t>2005-11-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2920,37 +2808,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H66" t="n">
-        <v>32</v>
-      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2702007</t>
+          <t>2604005</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Padmi Pertiwi</t>
+          <t>Hardi Utama</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2008-09-19</t>
+          <t>2006-10-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2958,19 +2844,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H67" t="n">
-        <v>17</v>
-      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2504007</t>
+          <t>2604006</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dian Palastri</t>
+          <t>Raihan Firmansyah</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2980,15 +2864,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2006-02-13</t>
+          <t>2008-08-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2996,19 +2880,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H68" t="n">
-        <v>40</v>
-      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2503005</t>
+          <t>2503004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salsabila Uyainah</t>
+          <t>Alika Wijayanti</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3026,7 +2908,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2005-12-02</t>
+          <t>2008-01-05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3034,24 +2916,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H69" t="n">
-        <v>29</v>
-      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2701008</t>
+          <t>2702006</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ajiono Wijaya</t>
+          <t>Pranawa Damanik</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3064,7 +2944,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2007-11-22</t>
+          <t>2006-10-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3072,24 +2952,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H70" t="n">
-        <v>23</v>
-      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2502007</t>
+          <t>2604007</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nardi Hutagalung</t>
+          <t>Rangga Widodo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3098,11 +2976,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2007-01-10</t>
+          <t>2006-12-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3115,17 +2993,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2702008</t>
+          <t>2701007</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jaeman Mansur</t>
+          <t>Prayoga Sinaga</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3138,7 +3016,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2008-10-31</t>
+          <t>2005-09-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3151,30 +3029,30 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2502008</t>
+          <t>2703008</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Narji Megantara</t>
+          <t>Salsabila Fujiati</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2006-02-23</t>
+          <t>2007-06-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3182,24 +3060,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H73" t="n">
-        <v>1</v>
-      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2702009</t>
+          <t>2603008</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mumpuni Mansur</t>
+          <t>Taswir Simbolon</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3208,11 +3084,11 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2008-04-26</t>
+          <t>2008-10-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3220,37 +3096,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H74" t="n">
-        <v>32</v>
-      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2602010</t>
+          <t>2504004</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ami Rahayu</t>
+          <t>Baktiono Widodo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2007-08-23</t>
+          <t>2008-04-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3258,19 +3132,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H75" t="n">
-        <v>8</v>
-      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2503006</t>
+          <t>2603009</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kamila Mulyani</t>
+          <t>Bakianto Wasita</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3280,15 +3152,15 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2007-03-18</t>
+          <t>2008-06-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3296,19 +3168,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H76" t="n">
-        <v>48</v>
-      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2501007</t>
+          <t>2601008</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ratna Melani</t>
+          <t>Siti Nasyidah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3322,11 +3192,11 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2007-06-05</t>
+          <t>2007-05-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3334,37 +3204,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H77" t="n">
-        <v>16</v>
-      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2701009</t>
+          <t>2504005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ganda Situmorang</t>
+          <t>Vicky Laksmiwati</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2006-10-29</t>
+          <t>2008-11-05</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3372,24 +3240,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H78" t="n">
-        <v>45</v>
-      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2703006</t>
+          <t>2504006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Umi Mayasari</t>
+          <t>Zulfa Novitasari</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3398,11 +3264,11 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2006-10-16</t>
+          <t>2007-08-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3410,24 +3276,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H79" t="n">
-        <v>37</v>
-      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2703007</t>
+          <t>2501004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Usman Simanjuntak</t>
+          <t>Hardi Halim</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3436,11 +3300,11 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2007-09-23</t>
+          <t>2006-11-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3448,37 +3312,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H80" t="n">
-        <v>26</v>
-      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2702010</t>
+          <t>2603010</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Karsa Nainggolan</t>
+          <t>Laila Widiastuti</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2008-07-11</t>
+          <t>2006-02-19</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3491,17 +3353,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2701010</t>
+          <t>2702007</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Natalia Utami</t>
+          <t>Ade Padmasari</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3514,7 +3376,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
+          <t>2008-07-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3522,37 +3384,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H82" t="n">
-        <v>26</v>
-      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2501008</t>
+          <t>2702008</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Zelaya Uyainah</t>
+          <t>Sidiq Utama</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2006-01-17</t>
+          <t>2007-02-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3565,12 +3425,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2603002</t>
+          <t>2703009</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ana Purnawati</t>
+          <t>Ifa Yolanda</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3584,11 +3444,11 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2007-11-16</t>
+          <t>2005-05-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3596,37 +3456,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H84" t="n">
-        <v>33</v>
-      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2602011</t>
+          <t>2701008</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Irsad Ramadan</t>
+          <t>Jasmin Suartini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2005-08-04</t>
+          <t>2007-08-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3634,37 +3492,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H85" t="n">
-        <v>11</v>
-      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2503007</t>
+          <t>2702009</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gangsar Jailani</t>
+          <t>Ifa Yulianti</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2005-01-15</t>
+          <t>2006-07-19</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3672,19 +3528,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H86" t="n">
-        <v>28</v>
-      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2601008</t>
+          <t>2501005</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Galih Saefullah</t>
+          <t>Kamila Nurdiyanti</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3694,15 +3548,15 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2008-06-14</t>
+          <t>2007-05-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3710,19 +3564,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H87" t="n">
-        <v>21</v>
-      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2602012</t>
+          <t>2702010</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Melinda Andriani</t>
+          <t>Paulin Yuliarti</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3736,11 +3588,11 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2008-02-03</t>
+          <t>2008-07-05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3748,37 +3600,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H88" t="n">
-        <v>21</v>
-      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2704006</t>
+          <t>2602009</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ilsa Nuraini</t>
+          <t>Darman Marbun</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2005-09-05</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3786,37 +3636,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H89" t="n">
-        <v>8</v>
-      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2701011</t>
+          <t>2503005</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gawati Puspasari</t>
+          <t>Caturangga Santoso</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2005-07-30</t>
+          <t>2007-05-07</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3824,24 +3672,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H90" t="n">
-        <v>47</v>
-      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2704007</t>
+          <t>2503006</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cawisadi Napitupulu</t>
+          <t>Balamantri Megantara</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3850,11 +3696,11 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2005-04-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3867,12 +3713,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2603003</t>
+          <t>2603011</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Yuliana Handayani</t>
+          <t>Ratih Utami</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3890,7 +3736,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2008-03-31</t>
+          <t>2007-09-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3898,24 +3744,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H92" t="n">
-        <v>42</v>
-      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2704008</t>
+          <t>2702011</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Baktiono Pradana</t>
+          <t>Umar Saptono</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DKV</t>
+          <t>Informatika</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3928,7 +3772,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2007-09-02</t>
+          <t>2006-12-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3936,19 +3780,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H93" t="n">
-        <v>42</v>
-      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2704009</t>
+          <t>2704005</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nabila Laksita</t>
+          <t>Halim Zulkarnain</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3958,7 +3800,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -3966,7 +3808,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2008-02-19</t>
+          <t>2008-07-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3974,24 +3816,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H94" t="n">
-        <v>47</v>
-      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2502009</t>
+          <t>2703010</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Setya Maulana</t>
+          <t>Darmaji Budiman</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4000,11 +3840,11 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2006-04-26</t>
+          <t>2005-07-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4012,24 +3852,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H95" t="n">
-        <v>31</v>
-      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2703008</t>
+          <t>2504007</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dirja Saragih</t>
+          <t>Danu Wijaya</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4038,11 +3876,11 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2006-12-13</t>
+          <t>2006-05-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4050,24 +3888,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H96" t="n">
-        <v>38</v>
-      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2503008</t>
+          <t>2701009</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vero Santoso</t>
+          <t>Karma Nainggolan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Sistem Informasi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4076,11 +3912,11 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2005-04-03</t>
+          <t>2007-03-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4088,19 +3924,17 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H97" t="n">
-        <v>30</v>
-      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2602013</t>
+          <t>2502009</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Azalea Riyanti</t>
+          <t>Devi Anggraini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4114,11 +3948,11 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2008-11-16</t>
+          <t>2007-02-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4126,24 +3960,22 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H98" t="n">
-        <v>37</v>
-      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2702011</t>
+          <t>2703011</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Karsana Tamba</t>
+          <t>Jaswadi Pangestu</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4156,7 +3988,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2004-12-04</t>
+          <t>2005-03-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4164,37 +3996,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H99" t="n">
-        <v>34</v>
-      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2601009</t>
+          <t>2703012</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Clara Novitasari</t>
+          <t>Bagya Sitompul</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sistem Informasi</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2006-08-30</t>
+          <t>2007-12-07</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4202,37 +4032,35 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H100" t="n">
-        <v>33</v>
-      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2702012</t>
+          <t>2604008</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ayu Widiastuti</t>
+          <t>Kuncara Sihombing</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Informatika</t>
+          <t>DKV</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2008-08-13</t>
+          <t>2006-06-23</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4240,14 +4068,12 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H101" t="n">
-        <v>34</v>
-      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2799208</t>
+          <t>2799732</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4270,7 +4096,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1954-10-24</t>
+          <t>2014-04-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4278,9 +4104,7 @@
           <t>Aktif</t>
         </is>
       </c>
-      <c r="H102" t="n">
-        <v>51</v>
-      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
